--- a/calificaciones.xlsx
+++ b/calificaciones.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="27">
   <si>
     <t xml:space="preserve">Pregunta</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t xml:space="preserve">Nota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP-Final</t>
   </si>
   <si>
     <t xml:space="preserve">Alumna/o</t>
@@ -143,7 +146,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,6 +157,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4C7DC"/>
+        <bgColor rgb="FFCCCCFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -204,7 +213,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -234,10 +243,26 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -266,7 +291,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFB4C7DC"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -424,7 +449,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.41"/>
@@ -512,10 +537,13 @@
       <c r="M2" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="N2" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -531,54 +559,55 @@
       <c r="M3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="M4" s="3" t="n">
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="M4" s="7" t="n">
         <v>9</v>
       </c>
+      <c r="N4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>8</v>
+      <c r="A5" s="10" t="s">
+        <v>9</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="11" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="4" t="s">
@@ -599,7 +628,7 @@
       <c r="I5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="11" t="s">
         <v>3</v>
       </c>
       <c r="K5" s="4" t="s">
@@ -611,10 +640,13 @@
       <c r="M5" s="3" t="n">
         <v>9</v>
       </c>
+      <c r="N5" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>9</v>
+      <c r="A6" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>2</v>
@@ -628,7 +660,7 @@
       <c r="E6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G6" s="4" t="s">
@@ -646,16 +678,19 @@
       <c r="K6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="11" t="s">
         <v>3</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>9</v>
       </c>
+      <c r="N6" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>10</v>
+      <c r="A7" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -663,163 +698,171 @@
       <c r="C7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N9" s="9"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>7</v>
-      </c>
+      <c r="N10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>15</v>
+      <c r="A11" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
@@ -857,10 +900,13 @@
       <c r="M11" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="N11" s="1" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
-        <v>16</v>
+      <c r="A12" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>2</v>
@@ -871,7 +917,7 @@
       <c r="D12" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="11" t="s">
         <v>2</v>
       </c>
       <c r="F12" s="4" t="s">
@@ -892,16 +938,19 @@
       <c r="K12" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="L12" s="7" t="s">
-        <v>17</v>
+      <c r="L12" s="11" t="s">
+        <v>18</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>9</v>
       </c>
+      <c r="N12" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
-        <v>18</v>
+      <c r="A13" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>2</v>
@@ -912,14 +961,14 @@
       <c r="D13" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="11" t="s">
         <v>2</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>11</v>
+      <c r="G13" s="11" t="s">
+        <v>12</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>2</v>
@@ -939,10 +988,13 @@
       <c r="M13" s="3" t="n">
         <v>9</v>
       </c>
+      <c r="N13" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>2</v>
@@ -953,11 +1005,11 @@
       <c r="D14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>11</v>
+      <c r="E14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>12</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>2</v>
@@ -974,16 +1026,19 @@
       <c r="K14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="L14" s="7" t="s">
-        <v>7</v>
+      <c r="L14" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="N14" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>20</v>
+      <c r="A15" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>2</v>
@@ -991,8 +1046,8 @@
       <c r="C15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>7</v>
+      <c r="D15" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>3</v>
@@ -1021,100 +1076,105 @@
       <c r="M15" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="N15" s="1" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="M16" s="3" t="n">
+      <c r="A16" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="M16" s="7" t="n">
         <v>4</v>
       </c>
+      <c r="N16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="A17" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
-        <v>23</v>
+      <c r="A18" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="C18" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>3</v>
       </c>
       <c r="E18" s="4" t="s">
@@ -1129,25 +1189,28 @@
       <c r="H18" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I18" s="7" t="s">
-        <v>7</v>
+      <c r="I18" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="K18" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="L18" s="7" t="s">
+      <c r="K18" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L18" s="11" t="s">
         <v>3</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="N18" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
-        <v>24</v>
+      <c r="A19" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>2</v>
@@ -1185,10 +1248,13 @@
       <c r="M19" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="N19" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
-        <v>25</v>
+      <c r="A20" s="10" t="s">
+        <v>26</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>2</v>
@@ -1208,8 +1274,8 @@
       <c r="G20" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H20" s="7" t="s">
-        <v>7</v>
+      <c r="H20" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>2</v>
@@ -1224,6 +1290,9 @@
         <v>2</v>
       </c>
       <c r="M20" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N20" s="1" t="n">
         <v>10</v>
       </c>
     </row>

--- a/calificaciones.xlsx
+++ b/calificaciones.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="28">
   <si>
     <t xml:space="preserve">Pregunta</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t xml:space="preserve">TP-Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promedio</t>
   </si>
   <si>
     <t xml:space="preserve">Alumna/o</t>
@@ -449,7 +452,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.41"/>
@@ -540,10 +543,13 @@
       <c r="N2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="O2" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -560,7 +566,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>2</v>
@@ -572,7 +578,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>3</v>
@@ -598,11 +604,17 @@
       <c r="M4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="N4" s="9"/>
+      <c r="N4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <f aca="false">AVERAGE(M4:N4)</f>
+        <v>4.5</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>2</v>
@@ -642,11 +654,15 @@
       </c>
       <c r="N5" s="1" t="n">
         <v>10</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <f aca="false">AVERAGE(M5:N5)</f>
+        <v>9.5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>2</v>
@@ -686,11 +702,15 @@
       </c>
       <c r="N6" s="1" t="n">
         <v>10</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <f aca="false">AVERAGE(M6:N6)</f>
+        <v>9.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -699,10 +719,10 @@
         <v>3</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>3</v>
@@ -711,7 +731,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>2</v>
@@ -731,10 +751,14 @@
       <c r="N7" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="O7" s="1" t="n">
+        <f aca="false">AVERAGE(M7:N7)</f>
+        <v>9</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -755,7 +779,7 @@
         <v>2</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>2</v>
@@ -767,7 +791,7 @@
         <v>2</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>8</v>
@@ -775,10 +799,14 @@
       <c r="N8" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="O8" s="1" t="n">
+        <f aca="false">AVERAGE(M8:N8)</f>
+        <v>9</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>2</v>
@@ -816,11 +844,17 @@
       <c r="M9" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="N9" s="9"/>
+      <c r="N9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <f aca="false">AVERAGE(M9:N9)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>2</v>
@@ -829,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>3</v>
@@ -838,7 +872,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>2</v>
@@ -853,16 +887,22 @@
         <v>2</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="N10" s="9"/>
+      <c r="N10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <f aca="false">AVERAGE(M10:N10)</f>
+        <v>3.5</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
@@ -902,11 +942,15 @@
       </c>
       <c r="N11" s="1" t="n">
         <v>9</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <f aca="false">AVERAGE(M11:N11)</f>
+        <v>9.5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>2</v>
@@ -939,18 +983,22 @@
         <v>2</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>9</v>
       </c>
       <c r="N12" s="1" t="n">
         <v>10</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <f aca="false">AVERAGE(M12:N12)</f>
+        <v>9.5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>2</v>
@@ -968,7 +1016,7 @@
         <v>3</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>2</v>
@@ -990,11 +1038,15 @@
       </c>
       <c r="N13" s="1" t="n">
         <v>10</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <f aca="false">AVERAGE(M13:N13)</f>
+        <v>9.5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>2</v>
@@ -1006,10 +1058,10 @@
         <v>2</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>2</v>
@@ -1027,7 +1079,7 @@
         <v>2</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>8</v>
@@ -1035,10 +1087,14 @@
       <c r="N14" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="O14" s="1" t="n">
+        <f aca="false">AVERAGE(M14:N14)</f>
+        <v>9</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>2</v>
@@ -1047,7 +1103,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>3</v>
@@ -1079,19 +1135,23 @@
       <c r="N15" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="O15" s="1" t="n">
+        <f aca="false">AVERAGE(M15:N15)</f>
+        <v>9</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>2</v>
@@ -1109,7 +1169,7 @@
         <v>3</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K16" s="8" t="s">
         <v>2</v>
@@ -1120,11 +1180,17 @@
       <c r="M16" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="N16" s="9"/>
+      <c r="N16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <f aca="false">AVERAGE(M16:N16)</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>2</v>
@@ -1157,22 +1223,28 @@
         <v>2</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="N17" s="9"/>
+      <c r="N17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <f aca="false">AVERAGE(M17:N17)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>3</v>
@@ -1190,13 +1262,13 @@
         <v>2</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L18" s="11" t="s">
         <v>3</v>
@@ -1207,10 +1279,14 @@
       <c r="N18" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="O18" s="1" t="n">
+        <f aca="false">AVERAGE(M18:N18)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>2</v>
@@ -1249,12 +1325,16 @@
         <v>10</v>
       </c>
       <c r="N19" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <f aca="false">AVERAGE(M19:N19)</f>
         <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>2</v>
@@ -1275,7 +1355,7 @@
         <v>2</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>2</v>
@@ -1293,6 +1373,10 @@
         <v>10</v>
       </c>
       <c r="N20" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <f aca="false">AVERAGE(M20:N20)</f>
         <v>10</v>
       </c>
     </row>
